--- a/docs/files-completion-list/ui-page-gap-register.xlsx
+++ b/docs/files-completion-list/ui-page-gap-register.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Register" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orphaned Endpoints" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dead Links" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="verification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Register" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orphaned Endpoints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dead Links" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Page Register'!$A$1:$N$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Orphaned Endpoints'!$A$1:$G$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dead Links'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Register'!$A$1:$N$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Orphaned Endpoints'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dead Links'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +54,18 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +132,21 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -148,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -217,6 +243,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1167,6 +1244,1194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Phase 6 Exit Verification — Frontend UI Page Gap</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Verified 2026-08-11, after Session 6-12 closed and before Session 7-1 started. Independent re-audit of the live working tree — NOT a reading of the close-out claims. Method: re-enumerated app/**/page.tsx (84 files) and app/api/**/route.ts (127 endpoints); re-ran the mock-data, dead-link and orphaned-endpoint scans that produced the original 2026-08-10 findings; re-checked every A1/A2/B/C row in phase-6-frontend-gap-matrix.md against code at file:line.</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="n"/>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>OVERALL VERDICT</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="n"/>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>NOT ZERO-GAP — 1 unbuilt page carrying a false BUILT claim, 1 partial, 1 deferred by decision, 4 orphaned endpoints</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Phase 6 delivered overwhelmingly: 55 of 59 matrix rows verified genuinely closed, all 4 flags resolved, every headline finding from 2026-08-10 fixed. But the literal claim 'all 59 rows triaged as BUILT / VERIFIED / OUT_OF_SCOPE' does not hold for row A2-12: it is recorded BUILT (Session 6-5) and the page does not exist. This is the LESSONS-LEARNED L11/L27 drift class the process exists to catch — recommend closing it before Phase 7 opens.</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="n"/>
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="30" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>HEADLINE FINDINGS — 2026-08-10 baseline vs. now</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Finding (2026-08-10)</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Then</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Evidence checked</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Pages rendering fabricated data in production</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>3 pages</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>0 pages</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>Scanned all 84 page.tsx for mock/MOCK/hardcoded data constants — zero hits. /settings/billing now has 4 real fetch calls (invoices, subscription, subscription/cancel, alerts); MOCK_ALERT count in fraud detail = 0</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Dead internal links</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>Every internal href in app/ + components/ resolved against the live route tree incl. dynamic segments — all resolve</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>app/not-found.tsx missing</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>app/not-found.tsx + app/global-error.tsx both exist</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>GET /api/geo/detect called but route absent</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>app/api/geo/detect/route.ts exists; F61 RESOLVED (Session 6-8)</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Admin split across two incompatible trees</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>15 + 8 pages, 19 unreachable</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>29 pages, one tree</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>app/admin/ page count = 0; app/(dashboard)/admin/ = 29; admin nav = 12 entries covering every section. F62 RESOLVED (Session 6-2)</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Orphaned endpoints / models with no UI</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>See 'Remaining orphaned endpoints' below — 2 deliberate, 2 need triage</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Public/legal pages missing</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>10 dead links</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>12 pages live</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>/about /docs /blog /changelog /careers /disclaimer /terms /privacy /help /affiliate /affiliate/join /status all exist. F63 RESOLVED (Session 6-10)</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>app/test-api scratch page</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>deleted</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>app/test-api/page.tsx no longer exists</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Total page count</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>57 (incl. test-api)</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>+27 net pages</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>ITEMS NOT CLOSED — action required before Phase 7</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Row ID</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>A2-12</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>/settings/security/activity — security activity log</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>Matrix records 'BUILT (Session 6-5)'. VERIFIED FALSE: the page does not exist; the SecurityAlert Prisma model still has ZERO UI consumers (only lib/security/device-detection.ts writes it); no /api/user/security-alerts endpoint exists either. Session 6-5's own order never scoped it — the only A1-9 mention is a passing note that 2FA management 'already exists'. Users are emailed about password changes and 2FA events they can never review in-product.</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>Correct the matrix row to OPEN, then either build the page in a small follow-up session or have Davin re-triage it OUT_OF_SCOPE. Do not leave a false BUILT claim standing — it will be read as truth by Phase 7 and beyond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>A1-9</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>/settings/security — login history + SecurityAlert</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>Recorded BUILT (Session 6-5). The 2FA half was genuinely fixed (dummy widget replaced with the real implementation). The other two sub-items were not: login history is still hard-capped at fetch('/api/user/login-history?limit=20') at line 177 with no pagination, no view-all, no offset; SecurityAlert is still not surfaced (grep count = 0 on the page).</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>Same fix as #1 — these are one piece of work. Downgrade the row to PARTIAL and either finish or re-triage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>B2-13</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>/welcome — first-run onboarding</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>Correctly triaged OUT_OF_SCOPE (Ticketed) by Davin — this is a decision, not a defect. Recorded here only so 'zero gap' is not claimed without qualification. The matrix itself flags it as not fitting the Step 3 session table.</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>No action. Confirm it carries into a Phase 9 / backlog ticket so it is not silently lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>REMAINING ORPHANED ENDPOINTS (4 of the original 32)</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Recommended action</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr"/>
+      <c r="F27" s="31" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>POST /api/checkout/validate-code</t>
+        </is>
+      </c>
+      <c r="B28" s="38" t="inlineStr">
+        <is>
+          <t>BY DESIGN</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>Deliberately left orphaned. Davin's live correction at Session 6-8 CONFIRM: DiscountCodeInput already has a working consumer of a DIFFERENT endpoint (dLocal validate-discount), so wiring this one as originally ordered would have been redundant. Recorded in the 6-8 order's entry criteria.</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>None — decision is documented and sound. Optionally retire the endpoint in Phase 8's deletion sweep.</t>
+        </is>
+      </c>
+      <c r="E28" s="33" t="inlineStr"/>
+      <c r="F28" s="33" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>GET /api/payments/dlocal/exchange-rate</t>
+        </is>
+      </c>
+      <c r="B29" s="38" t="inlineStr">
+        <is>
+          <t>BY DESIGN</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>Same decision, same session. PriceDisplay uses /convert, which returns localAmount server-side; using exchange-rate would have forced client-side multiplication, violating 6-8's own Service-Returned Math Rule.</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>None — decision is documented and sound. Candidate for Phase 8 deletion sweep.</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr"/>
+      <c r="F29" s="33" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>GET /api/affiliate/profile/payment</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>Became orphaned as a CONSEQUENCE of A1-16 being built correctly: /affiliate/dashboard/profile/payment is now a 16-line transparent redirect to /affiliate/settings/payout, so nothing calls the legacy endpoint any more. Benign, but not deliberate — no order recorded this as an intended outcome.</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>Triage explicitly: retire in Phase 8, or keep if any external caller depends on it.</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr"/>
+      <c r="F30" s="33" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>GET /api/disbursement/reports/affiliate/[affiliateId]  (+ .../affiliates/[id]/commissions)</t>
+        </is>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>A2-7 cited THREE endpoints as its backing evidence; the page built at /admin/disbursement/affiliates/[affiliateId] calls only /api/disbursement/affiliates/[affiliateId]. The reports/affiliate and /commissions endpoints remain unconsumed, so A2-7's row is narrower in reality than its evidence implied.</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>Confirm whether the built page is intentionally scoped narrower, or whether it should also surface the report + commissions data. Low risk either way.</t>
+        </is>
+      </c>
+      <c r="E31" s="33" t="inlineStr"/>
+      <c r="F31" s="33" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="n"/>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>SPOT-CHECKED BUILT CLAIMS — all confirmed genuine</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Verified how</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr"/>
+      <c r="F34" s="31" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>A1-1</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>/settings/billing wired to real endpoints</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>4 fetch calls present: /api/invoices, /api/subscription, /api/subscription/cancel, /api/alerts</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E35" s="33" t="inlineStr"/>
+      <c r="F35" s="33" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>A1-2</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>/admin/fraud-alerts/[id] wired</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>Calls /api/admin/fraud-alerts/${alertId}; MOCK_ALERT occurrences = 0</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E36" s="33" t="inlineStr"/>
+      <c r="F36" s="33" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>A1-4</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>/settings grid links all 9 subpages</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>9 distinct /settings/* hrefs found (was 4)</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr"/>
+      <c r="F37" s="33" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>A1-5</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>WISE option in disbursement config</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>8 occurrences of WISE in the config page (was 0)</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr"/>
+      <c r="F38" s="33" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>A1-11</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>3 orphan /api/tier/* endpoints wired</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>alert-form.tsx lines 145, 146, 196 — symbols, combinations, check/[symbol]</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr"/>
+      <c r="F39" s="33" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>A1-12</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>Dead nav links removed</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>/analytics and /indicators occurrences in sidebar.tsx + mobile-nav.tsx = 0</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="inlineStr"/>
+      <c r="F40" s="33" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>A1-14</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>Per-code cancel wired</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>code-inventory page line 112 calls /api/admin/codes/${code}/cancel</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E41" s="33" t="inlineStr"/>
+      <c r="F41" s="33" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>A1-16</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Legacy affiliate payment page retired</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>Now a 16-line transparent redirect() to /affiliate/settings/payout</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E42" s="33" t="inlineStr"/>
+      <c r="F42" s="33" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>A2-1…A2-11</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>11 new code-backed pages exist</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>All 11 routes present in the live route tree</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E43" s="33" t="inlineStr"/>
+      <c r="F43" s="33" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>B2-16…B2-19</t>
+        </is>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>4 admin system-ops pages exist</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>terminals, jobs, outbox, config-history all present; OutboxEvent / SystemConfigHistory / WiseTransfer / TrialStatus now all have UI consumers</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E44" s="33" t="inlineStr"/>
+      <c r="F44" s="33" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="n"/>
+      <c r="B45" s="26" t="n"/>
+      <c r="C45" s="26" t="n"/>
+      <c r="D45" s="30" t="n"/>
+      <c r="E45" s="26" t="n"/>
+      <c r="F45" s="26" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>FLAG STATUS</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n"/>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="28" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>Resolved in</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr"/>
+      <c r="F47" s="31" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>Frontend gap-matrix triage</t>
+        </is>
+      </c>
+      <c r="C48" s="40" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>Session 6-12 (Davin) — 59 rows triaged. NOTE: row A2-12's verdict is factually wrong (see Items Not Closed #1)</t>
+        </is>
+      </c>
+      <c r="E48" s="33" t="inlineStr"/>
+      <c r="F48" s="33" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>GET /api/geo/detect missing</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
+        <is>
+          <t>Session 6-8 (Davin) — built as a thin wrapper around the existing detectCountry()</t>
+        </is>
+      </c>
+      <c r="E49" s="33" t="inlineStr"/>
+      <c r="F49" s="33" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>F62</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>Admin IA split across two trees</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>Session 6-2 (Davin) — Option (a), merged into app/(dashboard)/admin/*, app/admin/ retired</t>
+        </is>
+      </c>
+      <c r="E50" s="33" t="inlineStr"/>
+      <c r="F50" s="33" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>F63</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>Public legal content ownership</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>Session 6-10 (Davin) — production-grade legal template copy shipped</t>
+        </is>
+      </c>
+      <c r="E51" s="33" t="inlineStr"/>
+      <c r="F51" s="33" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>F21</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>24h account-deletion GDPR gap</t>
+        </is>
+      </c>
+      <c r="C52" s="41" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>Pre-existing, NOT a Phase 6 item. Intersects the deletion pages built at 6-5 — still needs Davin's hard-delete vs anonymize decision</t>
+        </is>
+      </c>
+      <c r="E52" s="33" t="inlineStr"/>
+      <c r="F52" s="33" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="n"/>
+      <c r="B53" s="26" t="n"/>
+      <c r="C53" s="26" t="n"/>
+      <c r="D53" s="30" t="n"/>
+      <c r="E53" s="26" t="n"/>
+      <c r="F53" s="26" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>SCOPE &amp; LIMITS OF THIS VERIFICATION</t>
+        </is>
+      </c>
+      <c r="B54" s="28" t="n"/>
+      <c r="C54" s="28" t="n"/>
+      <c r="D54" s="28" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="28" t="n"/>
+    </row>
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>• STATIC ANALYSIS ONLY. This verifies that pages exist, endpoints have consumers, no mock-data constants remain, and every internal link resolves. It does NOT prove the pages render correctly, that the wired endpoints return the expected shapes at runtime, or that the UI behaves correctly for a real logged-in user.</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="n"/>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="30" t="n"/>
+      <c r="E55" s="26" t="n"/>
+      <c r="F55" s="26" t="n"/>
+    </row>
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>• NO LIVE BROWSER CHECK. Every Phase 6 session from 6-1b onward recorded the same standing gap (CLAUDE.md Waiting-on #117): no session ran a click-through against a real authenticated session, because CredentialsProvider was removed at Session 4B-21. That gap is unchanged and is the single largest residual risk in Phase 6's exit.</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="n"/>
+      <c r="C56" s="26" t="n"/>
+      <c r="D56" s="30" t="n"/>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="26" t="n"/>
+    </row>
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>• TEST SUITE NOT RE-RUN HERE. Last recorded by Session 6-12: 149/149 suites, 2322/2322 tests; tsc --noEmit clean; eslint with the same 4 pre-existing warnings. Re-measure at Session 7-1 CONFIRM rather than trusting this figure.</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="n"/>
+      <c r="C57" s="26" t="n"/>
+      <c r="D57" s="30" t="n"/>
+      <c r="E57" s="26" t="n"/>
+      <c r="F57" s="26" t="n"/>
+    </row>
+    <row r="58" ht="46" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>• ACCESSIBILITY / RESPONSIVE FIXES NOT INDEPENDENTLY RE-AUDITED. Session 6-12 reported 18 a11y fixes across 13 files and 8 responsive fixes across 6 files. Those were taken as reported; this verification did not re-derive them.</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="n"/>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="30" t="n"/>
+      <c r="E58" s="26" t="n"/>
+      <c r="F58" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5886,7 +7151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7067,7 +8332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/files-completion-list/ui-page-gap-register.xlsx
+++ b/docs/files-completion-list/ui-page-gap-register.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,11 @@
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -174,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -293,6 +298,18 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1244,21 +1261,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>Phase 6 Exit Verification — Frontend UI Page Gap</t>
+          <t>Phase 6 Exit Verification — Frontend UI Page Gap  ·  ROUND 2 (post ad-hoc repair)</t>
         </is>
       </c>
       <c r="B1" s="26" t="n"/>
@@ -1267,10 +1284,10 @@
       <c r="E1" s="26" t="n"/>
       <c r="F1" s="26" t="n"/>
     </row>
-    <row r="2" ht="58" customHeight="1">
+    <row r="2" ht="62" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>Verified 2026-08-11, after Session 6-12 closed and before Session 7-1 started. Independent re-audit of the live working tree — NOT a reading of the close-out claims. Method: re-enumerated app/**/page.tsx (84 files) and app/api/**/route.ts (127 endpoints); re-ran the mock-data, dead-link and orphaned-endpoint scans that produced the original 2026-08-10 findings; re-checked every A1/A2/B/C row in phase-6-frontend-gap-matrix.md against code at file:line.</t>
+          <t>Round 1 verified 2026-08-11 after Session 6-12 closed — found NOT ZERO-GAP (1 unbuilt page carrying a false BUILT claim, 1 partial, 1 deferred, 4 orphaned endpoints). An ad-hoc repair session was run per EXECUTOR-PROTOCOL §6. Round 2 (this sheet) re-verifies the live working tree after that repair. Method unchanged: independent re-enumeration of app/**/page.tsx (85) and app/api/**/route.ts (129), fresh mock-data / dead-link / orphaned-endpoint scans, and per-claim checks at file:line. The Executor's close-out report was NOT taken on trust — every claim below was re-derived.</t>
         </is>
       </c>
       <c r="B2" s="26" t="n"/>
@@ -1300,9 +1317,9 @@
       <c r="F4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
-        <is>
-          <t>NOT ZERO-GAP — 1 unbuilt page carrying a false BUILT claim, 1 partial, 1 deferred by decision, 4 orphaned endpoints</t>
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>ZERO UNACCOUNTED GAP — every item is now either closed in code, or carries an explicit recorded decision</t>
         </is>
       </c>
       <c r="B5" s="26" t="n"/>
@@ -1311,10 +1328,10 @@
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="62" customHeight="1">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Phase 6 delivered overwhelmingly: 55 of 59 matrix rows verified genuinely closed, all 4 flags resolved, every headline finding from 2026-08-10 fixed. But the literal claim 'all 59 rows triaged as BUILT / VERIFIED / OUT_OF_SCOPE' does not hold for row A2-12: it is recorded BUILT (Session 6-5) and the page does not exist. This is the LESSONS-LEARNED L11/L27 drift class the process exists to catch — recommend closing it before Phase 7 opens.</t>
+          <t>The false BUILT claim is gone: A2-12 was built for real and A1-9 completed. All 4 remaining orphaned endpoints now carry documented dispositions (2 resolved by design at Session 6-8; 2 recorded KEEP — retire in Phase 8). Two items remain open by DECISION, not by oversight: B2-13 /welcome (ticketed OUT_OF_SCOPE) and the operation-service Railway deploy (correctly escalated per §7, not performed unilaterally). Neither is a defect. NOTE: 'zero gap' is a static-analysis verdict — see Scope &amp; Limits.</t>
         </is>
       </c>
       <c r="B6" s="26" t="n"/>
@@ -1334,7 +1351,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>HEADLINE FINDINGS — 2026-08-10 baseline vs. now</t>
+          <t>ROUND 1 FINDINGS — disposition after the ad-hoc repair</t>
         </is>
       </c>
       <c r="B8" s="28" t="n"/>
@@ -1346,7 +1363,7 @@
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Finding (2026-08-10)</t>
+          <t>Round 1 finding</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
@@ -1366,7 +1383,7 @@
       </c>
       <c r="E9" s="31" t="inlineStr">
         <is>
-          <t>Evidence checked</t>
+          <t>Evidence re-derived this round</t>
         </is>
       </c>
       <c r="F9" s="31" t="inlineStr"/>
@@ -1374,17 +1391,17 @@
     <row r="10">
       <c r="A10" s="32" t="inlineStr">
         <is>
-          <t>Pages rendering fabricated data in production</t>
+          <t>A2-12 /settings/security/activity marked BUILT but did not exist</t>
         </is>
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>3 pages</t>
+          <t>OPEN (false claim)</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>0 pages</t>
+          <t>Built for real</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
@@ -1394,7 +1411,7 @@
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
-          <t>Scanned all 84 page.tsx for mock/MOCK/hardcoded data constants — zero hits. /settings/billing now has 4 real fetch calls (invoices, subscription, subscription/cancel, alerts); MOCK_ALERT count in fraud detail = 0</t>
+          <t>app/(dashboard)/settings/security/activity/page.tsx exists (12,599 bytes). Matrix row now reads 'BUILT (ad-hoc, 2026-08-11)' and explicitly records that it was wrongly marked BUILT (Session 6-5) at 6-12.</t>
         </is>
       </c>
       <c r="F10" s="33" t="inlineStr"/>
@@ -1402,17 +1419,17 @@
     <row r="11">
       <c r="A11" s="32" t="inlineStr">
         <is>
-          <t>Dead internal links</t>
+          <t>SecurityAlert model had zero UI consumers</t>
         </is>
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0 consumers</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2 consumers</t>
         </is>
       </c>
       <c r="D11" s="34" t="inlineStr">
@@ -1422,7 +1439,7 @@
       </c>
       <c r="E11" s="33" t="inlineStr">
         <is>
-          <t>Every internal href in app/ + components/ resolved against the live route tree incl. dynamic segments — all resolve</t>
+          <t>settings/security/activity/page.tsx + settings/security/page.tsx. Endpoints now exist on BOTH sides: operation-service UsersController @Get('security-alerts') L179 + @Post('security-alerts/:id/read') L191; monolith app/api/user/security-alerts/route.ts + [id]/read/route.ts.</t>
         </is>
       </c>
       <c r="F11" s="33" t="inlineStr"/>
@@ -1430,17 +1447,17 @@
     <row r="12">
       <c r="A12" s="32" t="inlineStr">
         <is>
-          <t>app/not-found.tsx missing</t>
+          <t>operation-service mirrored SecurityAlert was a narrow subset</t>
         </is>
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>missing 3 fields</t>
         </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>widened</t>
         </is>
       </c>
       <c r="D12" s="34" t="inlineStr">
@@ -1450,7 +1467,7 @@
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
-          <t>app/not-found.tsx + app/global-error.tsx both exist</t>
+          <t>deviceInfo, read, readAt all present in operation-service/prisma/schema.prisma, plus @@index([userId, read]). Additive only — this was the trap flagged before the build started, and it was handled.</t>
         </is>
       </c>
       <c r="F12" s="33" t="inlineStr"/>
@@ -1458,17 +1475,17 @@
     <row r="13">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>GET /api/geo/detect called but route absent</t>
+          <t>A1-9 login-history capped at limit=20, no pagination</t>
         </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>hardcoded cap</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>paginated</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
@@ -1478,7 +1495,7 @@
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>app/api/geo/detect/route.ts exists; F61 RESOLVED (Session 6-8)</t>
+          <t>fetchLoginHistory(offset, append) at L179; fetch uses ?limit=20&amp;offset=${offset} at L188; handleLoadMoreHistory at L208 wired to a Load more control at L1160; 'View All Activity' link added.</t>
         </is>
       </c>
       <c r="F13" s="33" t="inlineStr"/>
@@ -1486,17 +1503,17 @@
     <row r="14">
       <c r="A14" s="32" t="inlineStr">
         <is>
-          <t>Admin split across two incompatible trees</t>
+          <t>Real bug found during the repair (not in Round 1)</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>15 + 8 pages, 19 unreachable</t>
+          <t>latent</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>29 pages, one tree</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
@@ -1506,7 +1523,7 @@
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
-          <t>app/admin/ page count = 0; app/(dashboard)/admin/ = 29; admin nav = 12 entries covering every section. F62 RESOLVED (Session 6-2)</t>
+          <t>Refresh was onClick={fetchLoginHistory}, which would have passed the click event object as the offset argument. Now onClick={() =&gt; fetchLoginHistory()} at L1047. Found by the Executor, not by either audit.</t>
         </is>
       </c>
       <c r="F14" s="33" t="inlineStr"/>
@@ -1514,27 +1531,27 @@
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>Orphaned endpoints / models with no UI</t>
+          <t>OpenAPI specs would not have covered the new endpoint</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>See 'Remaining orphaned endpoints' below — 2 deliberate, 2 need triage</t>
+          <t>part-13-settings-openapi.yaml (2 refs) and part-22-user-account-openapi.yaml (5 refs). Load-bearing: Phase 7 generates its unified client FROM these specs.</t>
         </is>
       </c>
       <c r="F15" s="33" t="inlineStr"/>
@@ -1542,17 +1559,17 @@
     <row r="16">
       <c r="A16" s="32" t="inlineStr">
         <is>
-          <t>Public/legal pages missing</t>
+          <t>4 orphaned endpoints, 2 undecided</t>
         </is>
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>10 dead links</t>
+          <t>2 undecided</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>12 pages live</t>
+          <t>all 4 decided</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
@@ -1562,7 +1579,7 @@
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>/about /docs /blog /changelog /careers /disclaimer /terms /privacy /help /affiliate /affiliate/join /status all exist. F63 RESOLVED (Session 6-10)</t>
+          <t>Same 4 endpoints remain unconsumed, but all now carry recorded decisions — see the next block.</t>
         </is>
       </c>
       <c r="F16" s="33" t="inlineStr"/>
@@ -1570,17 +1587,17 @@
     <row r="17">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>app/test-api scratch page</t>
+          <t>Ownership scoping on the new endpoints</t>
         </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>deleted</t>
+          <t>scoped</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
@@ -1590,180 +1607,150 @@
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>app/test-api/page.tsx no longer exists</t>
+          <t>Both handlers derive the user from request.user.id (L187, L199) rather than trusting a caller-supplied id — no cross-user enumeration.</t>
         </is>
       </c>
       <c r="F17" s="33" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>Total page count</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>57 (incl. test-api)</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="E18" s="33" t="inlineStr">
-        <is>
-          <t>+27 net pages</t>
-        </is>
-      </c>
-      <c r="F18" s="33" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="n"/>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>ITEMS NOT CLOSED — action required before Phase 7</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="n"/>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>THE 4 REMAINING ORPHANED ENDPOINTS — all now carry an explicit decision</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Decided by / when</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Action owner</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr"/>
+      <c r="F20" s="31" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>Row ID</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-      <c r="F21" s="31" t="inlineStr">
-        <is>
-          <t>What to do</t>
-        </is>
-      </c>
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>POST /api/checkout/validate-code</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>BY DESIGN</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>Davin, live at Session 6-8 CONFIRM — DiscountCodeInput already consumes a different, working endpoint</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>Optional Phase 8 deletion sweep</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr"/>
+      <c r="F21" s="33" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>A2-12</t>
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>GET /api/payments/dlocal/exchange-rate</t>
+        </is>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>BY DESIGN</t>
         </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>/settings/security/activity — security activity log</t>
-        </is>
-      </c>
-      <c r="D22" s="36" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>Matrix records 'BUILT (Session 6-5)'. VERIFIED FALSE: the page does not exist; the SecurityAlert Prisma model still has ZERO UI consumers (only lib/security/device-detection.ts writes it); no /api/user/security-alerts endpoint exists either. Session 6-5's own order never scoped it — the only A1-9 mention is a passing note that 2FA management 'already exists'. Users are emailed about password changes and 2FA events they can never review in-product.</t>
-        </is>
-      </c>
-      <c r="F22" s="33" t="inlineStr">
-        <is>
-          <t>Correct the matrix row to OPEN, then either build the page in a small follow-up session or have Davin re-triage it OUT_OF_SCOPE. Do not leave a false BUILT claim standing — it will be read as truth by Phase 7 and beyond.</t>
-        </is>
-      </c>
+          <t>Davin, live at Session 6-8 CONFIRM — PriceDisplay uses /convert, which returns localAmount server-side; using exchange-rate would force client-side math and violate 6-8's Service-Returned Math Rule</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>Optional Phase 8 deletion sweep</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr"/>
+      <c r="F22" s="33" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>A1-9</t>
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>GET /api/affiliate/profile/payment</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>DECIDED</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>/settings/security — login history + SecurityAlert</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="E23" s="33" t="inlineStr">
-        <is>
-          <t>Recorded BUILT (Session 6-5). The 2FA half was genuinely fixed (dummy widget replaced with the real implementation). The other two sub-items were not: login history is still hard-capped at fetch('/api/user/login-history?limit=20') at line 177 with no pagination, no view-all, no offset; SecurityAlert is still not surfaced (grep count = 0 on the page).</t>
-        </is>
-      </c>
-      <c r="F23" s="33" t="inlineStr">
-        <is>
-          <t>Same fix as #1 — these are one piece of work. Downgrade the row to PARTIAL and either finish or re-triage.</t>
-        </is>
-      </c>
+          <t>Davin, ad-hoc 2026-08-11 (Decision B) — KEEP, retire in Phase 8's deletion sweep</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>Phase 8 — recorded in CLAUDE.md Waiting-on #130</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr"/>
+      <c r="F23" s="33" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>B2-13</t>
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>GET /api/disbursement/reports/affiliate/[affiliateId]  +  .../commissions</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>DECIDED</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>/welcome — first-run onboarding</t>
-        </is>
-      </c>
-      <c r="D24" s="37" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>Correctly triaged OUT_OF_SCOPE (Ticketed) by Davin — this is a decision, not a defect. Recorded here only so 'zero gap' is not claimed without qualification. The matrix itself flags it as not fitting the Step 3 session table.</t>
-        </is>
-      </c>
-      <c r="F24" s="33" t="inlineStr">
-        <is>
-          <t>No action. Confirm it carries into a Phase 9 / backlog ticket so it is not silently lost.</t>
-        </is>
-      </c>
+          <t>Davin, ad-hoc 2026-08-11 (Decision B) — KEEP, retire in Phase 8's deletion sweep</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>Phase 8 — recorded in CLAUDE.md Waiting-on #130</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr"/>
+      <c r="F24" s="33" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="30" t="n"/>
@@ -1776,7 +1763,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>REMAINING ORPHANED ENDPOINTS (4 of the original 32)</t>
+          <t>OPEN BY DECISION — not defects, but do not let them get lost</t>
         </is>
       </c>
       <c r="B26" s="28" t="n"/>
@@ -1788,638 +1775,460 @@
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>Endpoint</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Recommended action</t>
-        </is>
-      </c>
-      <c r="E27" s="31" t="inlineStr"/>
+          <t>Why it is open</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>Owner / when</t>
+        </is>
+      </c>
       <c r="F27" s="31" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>POST /api/checkout/validate-code</t>
-        </is>
-      </c>
-      <c r="B28" s="38" t="inlineStr">
-        <is>
-          <t>BY DESIGN</t>
-        </is>
-      </c>
-      <c r="C28" s="33" t="inlineStr">
-        <is>
-          <t>Deliberately left orphaned. Davin's live correction at Session 6-8 CONFIRM: DiscountCodeInput already has a working consumer of a DIFFERENT endpoint (dLocal validate-discount), so wiring this one as originally ordered would have been redundant. Recorded in the 6-8 order's entry criteria.</t>
+      <c r="A28" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>B2-13  /welcome  (first-run onboarding)</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
         <is>
-          <t>None — decision is documented and sound. Optionally retire the endpoint in Phase 8's deletion sweep.</t>
-        </is>
-      </c>
-      <c r="E28" s="33" t="inlineStr"/>
+          <t>Triaged OUT_OF_SCOPE (Ticketed) by Davin at 6-12. Confirmed still absent from the route tree. The matrix itself flags it as not fitting the Step 3 session table. A product decision, not an oversight.</t>
+        </is>
+      </c>
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>Davin — confirm it carries into a Phase 9 / backlog ticket</t>
+        </is>
+      </c>
       <c r="F28" s="33" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>GET /api/payments/dlocal/exchange-rate</t>
-        </is>
-      </c>
-      <c r="B29" s="38" t="inlineStr">
-        <is>
-          <t>BY DESIGN</t>
-        </is>
-      </c>
-      <c r="C29" s="33" t="inlineStr">
-        <is>
-          <t>Same decision, same session. PriceDisplay uses /convert, which returns localAmount server-side; using exchange-rate would have forced client-side multiplication, violating 6-8's own Service-Returned Math Rule.</t>
+      <c r="A29" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>operation-service Railway deploy for the new endpoints</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>CARRY-FORWARD</t>
         </is>
       </c>
       <c r="D29" s="32" t="inlineStr">
         <is>
-          <t>None — decision is documented and sound. Candidate for Phase 8 deletion sweep.</t>
-        </is>
-      </c>
-      <c r="E29" s="33" t="inlineStr"/>
+          <t>Correctly escalated per EXECUTOR-PROTOCOL §7 and NOT performed unilaterally. Verified safe to leave: shouldUseOperationServiceForUserSessions() returns true only when MIGRATE_USER_SESSIONS === 'true' (default off everywhere), and the monolith route carries a local-Prisma fallback — so the feature works today via the monolith. The operation-service half is built and tested but not yet reachable.</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>Davin — railway up --path-as-root --service operation-service, then flip the flag when ready</t>
+        </is>
+      </c>
       <c r="F29" s="33" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>GET /api/affiliate/profile/payment</t>
-        </is>
-      </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>Became orphaned as a CONSEQUENCE of A1-16 being built correctly: /affiliate/dashboard/profile/payment is now a 16-line transparent redirect to /affiliate/settings/payout, so nothing calls the legacy endpoint any more. Benign, but not deliberate — no order recorded this as an intended outcome.</t>
+      <c r="A30" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>No live authenticated browser click-through</t>
+        </is>
+      </c>
+      <c r="C30" s="44" t="inlineStr">
+        <is>
+          <t>CARRY-FORWARD</t>
         </is>
       </c>
       <c r="D30" s="32" t="inlineStr">
         <is>
-          <t>Triage explicitly: retire in Phase 8, or keep if any external caller depends on it.</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="inlineStr"/>
+          <t>Standing gap since Session 6-1b (CLAUDE.md Waiting-on #117) — CredentialsProvider was removed at 4B-21, so no session has run a click-through against a real logged-in user. The Executor did verify /settings/security/activity redirects unauthenticated traffic to /login?callbackUrl=..., proving the route compiles and the auth gate covers it.</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>Davin — one browser pass before Phase 7 would close the largest residual risk</t>
+        </is>
+      </c>
       <c r="F30" s="33" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>GET /api/disbursement/reports/affiliate/[affiliateId]  (+ .../affiliates/[id]/commissions)</t>
-        </is>
-      </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="C31" s="33" t="inlineStr">
-        <is>
-          <t>A2-7 cited THREE endpoints as its backing evidence; the page built at /admin/disbursement/affiliates/[affiliateId] calls only /api/disbursement/affiliates/[affiliateId]. The reports/affiliate and /commissions endpoints remain unconsumed, so A2-7's row is narrower in reality than its evidence implied.</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
-        <is>
-          <t>Confirm whether the built page is intentionally scoped narrower, or whether it should also surface the report + commissions data. Low risk either way.</t>
-        </is>
-      </c>
-      <c r="E31" s="33" t="inlineStr"/>
-      <c r="F31" s="33" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>SPOT-CHECKED BUILT CLAIMS — all confirmed genuine</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="n"/>
-      <c r="C33" s="28" t="n"/>
-      <c r="D33" s="28" t="n"/>
-      <c r="E33" s="28" t="n"/>
-      <c r="F33" s="28" t="n"/>
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="26" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>RECORD INTEGRITY — the point of the ad-hoc session</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>Artifact</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr"/>
+      <c r="E33" s="31" t="inlineStr"/>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="inlineStr">
-        <is>
-          <t>Claim</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>Verified how</t>
-        </is>
-      </c>
-      <c r="D34" s="31" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr"/>
-      <c r="F34" s="31" t="inlineStr"/>
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>phase-6-frontend-gap-matrix.md</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>A2-12 and A1-9 corrected; correction history recorded</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>YES — A2-12 now 'BUILT (ad-hoc 2026-08-11)' and states it was wrongly recorded BUILT (Session 6-5); A1-9 records exactly which sub-items shipped at 6-5 vs ad-hoc. KEEP decision recorded at line 207.</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr"/>
+      <c r="E34" s="33" t="inlineStr"/>
+      <c r="F34" s="33" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="32" t="inlineStr">
         <is>
-          <t>A1-1</t>
+          <t>DECISION-LOG.md  F11</t>
         </is>
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>/settings/billing wired to real endpoints</t>
-        </is>
-      </c>
-      <c r="C35" s="33" t="inlineStr">
-        <is>
-          <t>4 fetch calls present: /api/invoices, /api/subscription, /api/subscription/cancel, /api/alerts</t>
-        </is>
-      </c>
-      <c r="D35" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
+          <t>Appended, NOT reopened</t>
+        </is>
+      </c>
+      <c r="C35" s="45" t="inlineStr">
+        <is>
+          <t>YES — F11 remains RESOLVED (Session 6-12). The triage process was sound; one verdict was wrong. Appended twice: the correction, then the repair + Decision B.</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr"/>
       <c r="E35" s="33" t="inlineStr"/>
       <c r="F35" s="33" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="32" t="inlineStr">
         <is>
-          <t>A1-2</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>/admin/fraud-alerts/[id] wired</t>
-        </is>
-      </c>
-      <c r="C36" s="33" t="inlineStr">
-        <is>
-          <t>Calls /api/admin/fraud-alerts/${alertId}; MOCK_ALERT occurrences = 0</t>
-        </is>
-      </c>
-      <c r="D36" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
+          <t>Ad-hoc entry, phase/session unchanged</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="inlineStr">
+        <is>
+          <t>YES — labelled ad-hoc, Phase 6 stays CLOSED, Phase 7 has not opened. Decision B at L154-156; Waiting-on #130 added. 7-1 remains the next session.</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr"/>
       <c r="E36" s="33" t="inlineStr"/>
       <c r="F36" s="33" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="32" t="inlineStr">
         <is>
-          <t>A1-4</t>
+          <t>LESSONS-LEARNED.md</t>
         </is>
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>/settings grid links all 9 subpages</t>
-        </is>
-      </c>
-      <c r="C37" s="33" t="inlineStr">
-        <is>
-          <t>9 distinct /settings/* hrefs found (was 4)</t>
-        </is>
-      </c>
-      <c r="D37" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
+          <t>New rule harvested</t>
+        </is>
+      </c>
+      <c r="C37" s="45" t="inlineStr">
+        <is>
+          <t>YES — the triage-verdict-must-cite-evidence rule is present.</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr"/>
       <c r="E37" s="33" t="inlineStr"/>
       <c r="F37" s="33" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="32" t="inlineStr">
         <is>
-          <t>A1-5</t>
+          <t>Tests</t>
         </is>
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>WISE option in disbursement config</t>
-        </is>
-      </c>
-      <c r="C38" s="33" t="inlineStr">
-        <is>
-          <t>8 occurrences of WISE in the config page (was 0)</t>
-        </is>
-      </c>
-      <c r="D38" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
+          <t>New coverage alongside the code</t>
+        </is>
+      </c>
+      <c r="C38" s="45" t="inlineStr">
+        <is>
+          <t>YES — 4 new test files: __tests__/api/security-alerts.test.ts, security-alerts-id-read.test.ts, __tests__/pages/settings/security-activity.test.tsx, security-login-history-pagination.test.tsx</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr"/>
       <c r="E38" s="33" t="inlineStr"/>
       <c r="F38" s="33" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
-        <is>
-          <t>A1-11</t>
-        </is>
-      </c>
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t>3 orphan /api/tier/* endpoints wired</t>
-        </is>
-      </c>
-      <c r="C39" s="33" t="inlineStr">
-        <is>
-          <t>alert-form.tsx lines 145, 146, 196 — symbols, combinations, check/[symbol]</t>
-        </is>
-      </c>
-      <c r="D39" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E39" s="33" t="inlineStr"/>
-      <c r="F39" s="33" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="32" t="inlineStr">
-        <is>
-          <t>A1-12</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>Dead nav links removed</t>
-        </is>
-      </c>
-      <c r="C40" s="33" t="inlineStr">
-        <is>
-          <t>/analytics and /indicators occurrences in sidebar.tsx + mobile-nav.tsx = 0</t>
-        </is>
-      </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E40" s="33" t="inlineStr"/>
-      <c r="F40" s="33" t="inlineStr"/>
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="26" t="n"/>
+      <c r="F39" s="26" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>SURFACE COUNTS</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="32" t="inlineStr">
         <is>
-          <t>A1-14</t>
+          <t>Pages</t>
         </is>
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>Per-code cancel wired</t>
-        </is>
-      </c>
-      <c r="C41" s="33" t="inlineStr">
-        <is>
-          <t>code-inventory page line 112 calls /api/admin/codes/${code}/cancel</t>
-        </is>
-      </c>
-      <c r="D41" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E41" s="33" t="inlineStr"/>
-      <c r="F41" s="33" t="inlineStr"/>
+          <t>57 (2026-08-10 baseline)</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="32" t="inlineStr">
         <is>
-          <t>A1-16</t>
+          <t>API endpoints</t>
         </is>
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>Legacy affiliate payment page retired</t>
-        </is>
-      </c>
-      <c r="C42" s="33" t="inlineStr">
-        <is>
-          <t>Now a 16-line transparent redirect() to /affiliate/settings/payout</t>
-        </is>
-      </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E42" s="33" t="inlineStr"/>
-      <c r="F42" s="33" t="inlineStr"/>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D42" s="30" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="26" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="32" t="inlineStr">
         <is>
-          <t>A2-1…A2-11</t>
+          <t>Pages rendering mock data</t>
         </is>
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>11 new code-backed pages exist</t>
-        </is>
-      </c>
-      <c r="C43" s="33" t="inlineStr">
-        <is>
-          <t>All 11 routes present in the live route tree</t>
-        </is>
-      </c>
-      <c r="D43" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E43" s="33" t="inlineStr"/>
-      <c r="F43" s="33" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="26" t="n"/>
+      <c r="F43" s="26" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="32" t="inlineStr">
         <is>
-          <t>B2-16…B2-19</t>
+          <t>Dead internal links</t>
         </is>
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>4 admin system-ops pages exist</t>
-        </is>
-      </c>
-      <c r="C44" s="33" t="inlineStr">
-        <is>
-          <t>terminals, jobs, outbox, config-history all present; OutboxEvent / SystemConfigHistory / WiseTransfer / TrialStatus now all have UI consumers</t>
-        </is>
-      </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E44" s="33" t="inlineStr"/>
-      <c r="F44" s="33" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="26" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n"/>
-      <c r="B45" s="26" t="n"/>
-      <c r="C45" s="26" t="n"/>
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>Orphaned endpoints</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>4 (all decided)</t>
+        </is>
+      </c>
       <c r="D45" s="30" t="n"/>
       <c r="E45" s="26" t="n"/>
       <c r="F45" s="26" t="n"/>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>FLAG STATUS</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="n"/>
-      <c r="C46" s="28" t="n"/>
-      <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
-      <c r="F46" s="28" t="n"/>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>Gap-matrix rows unaccounted</t>
+        </is>
+      </c>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>1 (A2-12)</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="n"/>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="26" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="31" t="inlineStr">
-        <is>
-          <t>Flag</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C47" s="31" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D47" s="31" t="inlineStr">
-        <is>
-          <t>Resolved in</t>
-        </is>
-      </c>
-      <c r="E47" s="31" t="inlineStr"/>
-      <c r="F47" s="31" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="32" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t>Frontend gap-matrix triage</t>
-        </is>
-      </c>
-      <c r="C48" s="40" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="D48" s="32" t="inlineStr">
-        <is>
-          <t>Session 6-12 (Davin) — 59 rows triaged. NOTE: row A2-12's verdict is factually wrong (see Items Not Closed #1)</t>
-        </is>
-      </c>
-      <c r="E48" s="33" t="inlineStr"/>
-      <c r="F48" s="33" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="32" t="inlineStr">
-        <is>
-          <t>F61</t>
-        </is>
-      </c>
-      <c r="B49" s="33" t="inlineStr">
-        <is>
-          <t>GET /api/geo/detect missing</t>
-        </is>
-      </c>
-      <c r="C49" s="40" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="inlineStr">
-        <is>
-          <t>Session 6-8 (Davin) — built as a thin wrapper around the existing detectCountry()</t>
-        </is>
-      </c>
-      <c r="E49" s="33" t="inlineStr"/>
-      <c r="F49" s="33" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="32" t="inlineStr">
-        <is>
-          <t>F62</t>
-        </is>
-      </c>
-      <c r="B50" s="33" t="inlineStr">
-        <is>
-          <t>Admin IA split across two trees</t>
-        </is>
-      </c>
-      <c r="C50" s="40" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="inlineStr">
-        <is>
-          <t>Session 6-2 (Davin) — Option (a), merged into app/(dashboard)/admin/*, app/admin/ retired</t>
-        </is>
-      </c>
-      <c r="E50" s="33" t="inlineStr"/>
-      <c r="F50" s="33" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="32" t="inlineStr">
-        <is>
-          <t>F63</t>
-        </is>
-      </c>
-      <c r="B51" s="33" t="inlineStr">
-        <is>
-          <t>Public legal content ownership</t>
-        </is>
-      </c>
-      <c r="C51" s="40" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="inlineStr">
-        <is>
-          <t>Session 6-10 (Davin) — production-grade legal template copy shipped</t>
-        </is>
-      </c>
-      <c r="E51" s="33" t="inlineStr"/>
-      <c r="F51" s="33" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="32" t="inlineStr">
-        <is>
-          <t>F21</t>
-        </is>
-      </c>
-      <c r="B52" s="33" t="inlineStr">
-        <is>
-          <t>24h account-deletion GDPR gap</t>
-        </is>
-      </c>
-      <c r="C52" s="41" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="inlineStr">
-        <is>
-          <t>Pre-existing, NOT a Phase 6 item. Intersects the deletion pages built at 6-5 — still needs Davin's hard-delete vs anonymize decision</t>
-        </is>
-      </c>
-      <c r="E52" s="33" t="inlineStr"/>
-      <c r="F52" s="33" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="30" t="n"/>
-      <c r="B53" s="26" t="n"/>
-      <c r="C53" s="26" t="n"/>
-      <c r="D53" s="30" t="n"/>
-      <c r="E53" s="26" t="n"/>
-      <c r="F53" s="26" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>SCOPE &amp; LIMITS OF THIS VERIFICATION</t>
-        </is>
-      </c>
-      <c r="B54" s="28" t="n"/>
-      <c r="C54" s="28" t="n"/>
-      <c r="D54" s="28" t="n"/>
-      <c r="E54" s="28" t="n"/>
-      <c r="F54" s="28" t="n"/>
-    </row>
-    <row r="55" ht="46" customHeight="1">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>• STATIC ANALYSIS ONLY. This verifies that pages exist, endpoints have consumers, no mock-data constants remain, and every internal link resolves. It does NOT prove the pages render correctly, that the wired endpoints return the expected shapes at runtime, or that the UI behaves correctly for a real logged-in user.</t>
-        </is>
-      </c>
-      <c r="B55" s="26" t="n"/>
-      <c r="C55" s="26" t="n"/>
-      <c r="D55" s="30" t="n"/>
-      <c r="E55" s="26" t="n"/>
-      <c r="F55" s="26" t="n"/>
-    </row>
-    <row r="56" ht="46" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>• NO LIVE BROWSER CHECK. Every Phase 6 session from 6-1b onward recorded the same standing gap (CLAUDE.md Waiting-on #117): no session ran a click-through against a real authenticated session, because CredentialsProvider was removed at Session 4B-21. That gap is unchanged and is the single largest residual risk in Phase 6's exit.</t>
-        </is>
-      </c>
-      <c r="B56" s="26" t="n"/>
-      <c r="C56" s="26" t="n"/>
-      <c r="D56" s="30" t="n"/>
-      <c r="E56" s="26" t="n"/>
-      <c r="F56" s="26" t="n"/>
-    </row>
-    <row r="57" ht="46" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>• TEST SUITE NOT RE-RUN HERE. Last recorded by Session 6-12: 149/149 suites, 2322/2322 tests; tsc --noEmit clean; eslint with the same 4 pre-existing warnings. Re-measure at Session 7-1 CONFIRM rather than trusting this figure.</t>
-        </is>
-      </c>
-      <c r="B57" s="26" t="n"/>
-      <c r="C57" s="26" t="n"/>
-      <c r="D57" s="30" t="n"/>
-      <c r="E57" s="26" t="n"/>
-      <c r="F57" s="26" t="n"/>
-    </row>
-    <row r="58" ht="46" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>• ACCESSIBILITY / RESPONSIVE FIXES NOT INDEPENDENTLY RE-AUDITED. Session 6-12 reported 18 a11y fixes across 13 files and 8 responsive fixes across 6 files. Those were taken as reported; this verification did not re-derive them.</t>
-        </is>
-      </c>
-      <c r="B58" s="26" t="n"/>
-      <c r="C58" s="26" t="n"/>
-      <c r="D58" s="30" t="n"/>
-      <c r="E58" s="26" t="n"/>
-      <c r="F58" s="26" t="n"/>
+      <c r="A47" s="30" t="n"/>
+      <c r="B47" s="26" t="n"/>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="30" t="n"/>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="26" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>SCOPE &amp; LIMITS</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="n"/>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>• STATIC ANALYSIS ONLY. Verifies that pages exist, endpoints have consumers, no mock-data constants remain, every internal link resolves, and the record matches the code. Does NOT prove pages render correctly or that wired endpoints return the expected shapes at runtime.</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="30" t="n"/>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="26" t="n"/>
+    </row>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>• TEST SUITE NOT RE-RUN HERE. The Executor reported 153/153 suites, 2344/2344 tests (monolith) and 42/42, 393/393 (operation-service), tsc clean both, eslint with the same 4 pre-existing warnings. The 4 new test files were confirmed to exist; their results were not re-executed in this verification. Re-measure at Session 7-1 CONFIRM.</t>
+        </is>
+      </c>
+      <c r="B50" s="26" t="n"/>
+      <c r="C50" s="26" t="n"/>
+      <c r="D50" s="30" t="n"/>
+      <c r="E50" s="26" t="n"/>
+      <c r="F50" s="26" t="n"/>
+    </row>
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>• THE operation-service HALF IS UNDEPLOYED. Built, tested, spec'd — but not on Railway. Harmless today (flag off, monolith fallback serves the feature), but the two halves are not yet in sync in production.</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="30" t="n"/>
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="26" t="n"/>
+    </row>
+    <row r="52" ht="46" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>• PHASE 7 READINESS: the OpenAPI spec update was the load-bearing step here. Because both /api/user/* specs now document the new endpoints, Phase 7's generated unified client will include them without a regeneration cycle.</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="n"/>
+      <c r="C52" s="26" t="n"/>
+      <c r="D52" s="30" t="n"/>
+      <c r="E52" s="26" t="n"/>
+      <c r="F52" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/files-completion-list/ui-page-gap-register.xlsx
+++ b/docs/files-completion-list/ui-page-gap-register.xlsx
@@ -2431,12 +2431,12 @@
       </c>
       <c r="M3" s="13" t="inlineStr">
         <is>
-          <t>Calls GET /api/geo/detect which DOES NOT EXIST -&gt; 404 on every load. Create route or remove call + fall back to manual country select.</t>
+          <t>RESOLVED (Session 6-8): Built app/api/geo/detect/route.ts (HTTP 200 OK wrapper around lib/geo/detect-country.ts)</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
         <is>
-          <t>app/(marketing)/pricing/page.tsx:155</t>
+          <t>app/(marketing)/pricing/page.tsx &amp; app/api/geo/detect/route.ts</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,11 @@
       </c>
       <c r="L5" s="11" t="inlineStr"/>
       <c r="M5" s="13" t="inlineStr"/>
-      <c r="N5" s="13" t="inlineStr"/>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>app/(auth)/login/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -2646,7 +2650,11 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="13" t="inlineStr"/>
-      <c r="N7" s="13" t="inlineStr"/>
+      <c r="N7" s="13" t="inlineStr">
+        <is>
+          <t>app/(auth)/forgot-password/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -2692,7 +2700,11 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="13" t="inlineStr"/>
-      <c r="N8" s="13" t="inlineStr"/>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>app/(auth)/reset-password/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -2738,7 +2750,11 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="13" t="inlineStr"/>
-      <c r="N9" s="13" t="inlineStr"/>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>app/(auth)/verify-2fa/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -2784,7 +2800,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="13" t="inlineStr"/>
-      <c r="N10" s="13" t="inlineStr"/>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>app/(auth)/verify-email/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -2830,7 +2850,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="13" t="inlineStr"/>
-      <c r="N11" s="13" t="inlineStr"/>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>app/(auth)/verify-email/pending/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -3292,7 +3316,11 @@
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="13" t="inlineStr"/>
-      <c r="N20" s="13" t="inlineStr"/>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/settings/appearance/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -3446,7 +3474,11 @@
       <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="13" t="inlineStr"/>
-      <c r="N23" s="13" t="inlineStr"/>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/settings/language/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -3500,7 +3532,11 @@
           <t>Auth-gated only. A PUBLIC /privacy is needed for the marketing footer and the signup consent checkbox.</t>
         </is>
       </c>
-      <c r="N24" s="13" t="inlineStr"/>
+      <c r="N24" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/settings/privacy/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -3542,7 +3578,11 @@
       <c r="K25" s="11" t="inlineStr"/>
       <c r="L25" s="11" t="inlineStr"/>
       <c r="M25" s="13" t="inlineStr"/>
-      <c r="N25" s="13" t="inlineStr"/>
+      <c r="N25" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/settings/profile/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -3654,7 +3694,11 @@
           <t>Auth-gated only. A PUBLIC /terms is needed for the footer and signup consent.</t>
         </is>
       </c>
-      <c r="N27" s="13" t="inlineStr"/>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/settings/terms/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
@@ -3800,7 +3844,11 @@
       <c r="K30" s="11" t="inlineStr"/>
       <c r="L30" s="11" t="inlineStr"/>
       <c r="M30" s="13" t="inlineStr"/>
-      <c r="N30" s="13" t="inlineStr"/>
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/api-usage/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -3838,7 +3886,11 @@
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="11" t="inlineStr"/>
       <c r="M31" s="13" t="inlineStr"/>
-      <c r="N31" s="13" t="inlineStr"/>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/errors/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -3880,7 +3932,11 @@
           <t>List page is correctly wired to /api/admin/fraud-alerts</t>
         </is>
       </c>
-      <c r="N32" s="13" t="inlineStr"/>
+      <c r="N32" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/fraud-alerts/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
@@ -3922,7 +3978,11 @@
           <t>Wired to /api/disbursement/health, /reports/summary, /affiliates/payable</t>
         </is>
       </c>
-      <c r="N33" s="13" t="inlineStr"/>
+      <c r="N33" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
@@ -4014,7 +4074,11 @@
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr"/>
       <c r="M35" s="13" t="inlineStr"/>
-      <c r="N35" s="13" t="inlineStr"/>
+      <c r="N35" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/affiliates/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
@@ -4052,7 +4116,11 @@
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="13" t="inlineStr"/>
-      <c r="N36" s="13" t="inlineStr"/>
+      <c r="N36" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/audit/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
@@ -4090,7 +4158,11 @@
       <c r="K37" s="11" t="inlineStr"/>
       <c r="L37" s="11" t="inlineStr"/>
       <c r="M37" s="13" t="inlineStr"/>
-      <c r="N37" s="13" t="inlineStr"/>
+      <c r="N37" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/batches/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
@@ -4186,7 +4258,11 @@
           <t>Wired to /api/wise/recipients. Known UX gap: response carries no affiliate display name.</t>
         </is>
       </c>
-      <c r="N39" s="13" t="inlineStr"/>
+      <c r="N39" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/recipients/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
@@ -4224,7 +4300,11 @@
       <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="13" t="inlineStr"/>
-      <c r="N40" s="13" t="inlineStr"/>
+      <c r="N40" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/transactions/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
@@ -4262,7 +4342,11 @@
       <c r="K41" s="11" t="inlineStr"/>
       <c r="L41" s="11" t="inlineStr"/>
       <c r="M41" s="13" t="inlineStr"/>
-      <c r="N41" s="13" t="inlineStr"/>
+      <c r="N41" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/affiliates/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
@@ -4358,7 +4442,11 @@
           <t>Wired incl. /api/admin/commissions/pay</t>
         </is>
       </c>
-      <c r="N43" s="13" t="inlineStr"/>
+      <c r="N43" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/affiliates/reports/commission-owings/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n">
@@ -4396,7 +4484,11 @@
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="inlineStr"/>
       <c r="M44" s="13" t="inlineStr"/>
-      <c r="N44" s="13" t="inlineStr"/>
+      <c r="N44" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/affiliates/reports/profit-loss/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
@@ -4434,7 +4526,11 @@
       <c r="K45" s="11" t="inlineStr"/>
       <c r="L45" s="11" t="inlineStr"/>
       <c r="M45" s="13" t="inlineStr"/>
-      <c r="N45" s="13" t="inlineStr"/>
+      <c r="N45" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/affiliates/reports/sales-performance/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
@@ -4472,7 +4568,11 @@
       <c r="K46" s="11" t="inlineStr"/>
       <c r="L46" s="11" t="inlineStr"/>
       <c r="M46" s="13" t="inlineStr"/>
-      <c r="N46" s="13" t="inlineStr"/>
+      <c r="N46" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/settings/affiliate/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
@@ -4510,7 +4610,11 @@
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr"/>
       <c r="M47" s="13" t="inlineStr"/>
-      <c r="N47" s="13" t="inlineStr"/>
+      <c r="N47" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/dashboard/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n">
@@ -4548,7 +4652,11 @@
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="inlineStr"/>
       <c r="M48" s="13" t="inlineStr"/>
-      <c r="N48" s="13" t="inlineStr"/>
+      <c r="N48" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/dashboard/codes/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
@@ -4640,7 +4748,11 @@
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
       <c r="M50" s="13" t="inlineStr"/>
-      <c r="N50" s="13" t="inlineStr"/>
+      <c r="N50" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/dashboard/profile/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
@@ -4736,7 +4848,11 @@
           <t>Live Wise recipient flow</t>
         </is>
       </c>
-      <c r="N52" s="13" t="inlineStr"/>
+      <c r="N52" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/settings/payout/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
@@ -4778,7 +4894,11 @@
       </c>
       <c r="L53" s="11" t="inlineStr"/>
       <c r="M53" s="13" t="inlineStr"/>
-      <c r="N53" s="13" t="inlineStr"/>
+      <c r="N53" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/register/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -4820,7 +4940,11 @@
       </c>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="13" t="inlineStr"/>
-      <c r="N54" s="13" t="inlineStr"/>
+      <c r="N54" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/verify/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
@@ -4872,7 +4996,7 @@
       </c>
       <c r="N55" s="13" t="inlineStr">
         <is>
-          <t>app/admin/affiliates/[id]/page.tsx</t>
+          <t>app/(dashboard)/admin/affiliates/[id]/page.tsx</t>
         </is>
       </c>
     </row>
@@ -4926,7 +5050,7 @@
       </c>
       <c r="N56" s="13" t="inlineStr">
         <is>
-          <t>app/(dashboard)/admin/fraud-alerts/[id]/page.tsx:63,66,112</t>
+          <t>app/(dashboard)/admin/fraud-alerts/[id]/page.tsx</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5154,7 @@
       </c>
       <c r="N58" s="13" t="inlineStr">
         <is>
-          <t>app/test-api/page.tsx</t>
+          <t>app/test-api/</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5282,7 @@
       </c>
       <c r="N60" s="13" t="inlineStr">
         <is>
-          <t>app/api/user/account/deletion-confirm/route.ts</t>
+          <t>app/(public)/settings/account/delete/confirm/page.tsx</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5344,7 @@
       </c>
       <c r="N61" s="13" t="inlineStr">
         <is>
-          <t>app/api/user/account/deletion-cancel/route.ts</t>
+          <t>app/(public)/settings/account/delete/cancel/page.tsx</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5402,7 @@
       </c>
       <c r="N62" s="13" t="inlineStr">
         <is>
-          <t>app/checkout/page.tsx:160</t>
+          <t>app/checkout/return/page.tsx</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5514,7 @@
       </c>
       <c r="N64" s="13" t="inlineStr">
         <is>
-          <t>app/api/alerts/[id]/route.ts</t>
+          <t>app/(dashboard)/alerts/[id]/edit/page.tsx</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5676,7 @@
       </c>
       <c r="N67" s="13" t="inlineStr">
         <is>
-          <t>app/api/disbursement/reports/affiliate/[affiliateId]/route.ts</t>
+          <t>app/(dashboard)/admin/disbursement/affiliates/[affiliateId]/page.tsx</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5730,7 @@
       </c>
       <c r="N68" s="13" t="inlineStr">
         <is>
-          <t>prisma/non-market-data/schema.prisma</t>
+          <t>app/(dashboard)/admin/users/[id]/page.tsx</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5902,11 @@
           <t>Linked from marketing header - dead link</t>
         </is>
       </c>
-      <c r="N71" s="13" t="inlineStr"/>
+      <c r="N71" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/about/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
@@ -5836,7 +5964,11 @@
           <t>Linked from marketing footer - dead link</t>
         </is>
       </c>
-      <c r="N72" s="13" t="inlineStr"/>
+      <c r="N72" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/docs/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n">
@@ -5894,7 +6026,11 @@
           <t>Linked from marketing footer - dead link</t>
         </is>
       </c>
-      <c r="N73" s="13" t="inlineStr"/>
+      <c r="N73" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/blog/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n">
@@ -5952,7 +6088,11 @@
           <t>Linked from marketing footer - dead link</t>
         </is>
       </c>
-      <c r="N74" s="13" t="inlineStr"/>
+      <c r="N74" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/changelog/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n">
@@ -6010,7 +6150,11 @@
           <t>Linked from marketing footer - dead link</t>
         </is>
       </c>
-      <c r="N75" s="13" t="inlineStr"/>
+      <c r="N75" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/careers/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n">
@@ -6068,7 +6212,11 @@
           <t>Linked from marketing footer - dead link. COMPLIANCE-RELEVANT for a trading product.</t>
         </is>
       </c>
-      <c r="N76" s="13" t="inlineStr"/>
+      <c r="N76" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/disclaimer/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
@@ -6126,7 +6274,11 @@
           <t>Dead link from footer AND from the registration consent checkbox. /settings/terms exists but is auth-gated so it cannot serve either.</t>
         </is>
       </c>
-      <c r="N77" s="13" t="inlineStr"/>
+      <c r="N77" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/terms/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
@@ -6184,7 +6336,11 @@
           <t>Dead link from footer AND registration consent checkbox. /settings/privacy is auth-gated.</t>
         </is>
       </c>
-      <c r="N78" s="13" t="inlineStr"/>
+      <c r="N78" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/privacy/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n">
@@ -6242,7 +6398,11 @@
           <t>Linked from marketing footer - dead link</t>
         </is>
       </c>
-      <c r="N79" s="13" t="inlineStr"/>
+      <c r="N79" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/help/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -6300,7 +6460,11 @@
           <t>Linked from marketing header - dead link. No public pitch for the affiliate programme exists.</t>
         </is>
       </c>
-      <c r="N80" s="13" t="inlineStr"/>
+      <c r="N80" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n">
@@ -6358,7 +6522,11 @@
           <t>Linked from register-form.tsx:617 - dead link. Either build, or redirect to /affiliate/register.</t>
         </is>
       </c>
-      <c r="N81" s="13" t="inlineStr"/>
+      <c r="N81" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/join/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
@@ -6416,7 +6584,11 @@
           <t>Footer links to external status.tradingalerts.com</t>
         </is>
       </c>
-      <c r="N82" s="13" t="inlineStr"/>
+      <c r="N82" s="13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/status/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n">
@@ -6470,7 +6642,11 @@
           <t>No onboarding exists anywhere in the product today.</t>
         </is>
       </c>
-      <c r="N83" s="13" t="inlineStr"/>
+      <c r="N83" s="13" t="inlineStr">
+        <is>
+          <t>Pending Codebase Creation</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n">
@@ -6536,7 +6712,11 @@
           <t>THE APP HAS NO 404 PAGE - only app/error.tsx exists. With 14 dead internal links this is actively user-facing.</t>
         </is>
       </c>
-      <c r="N84" s="13" t="inlineStr"/>
+      <c r="N84" s="13" t="inlineStr">
+        <is>
+          <t>app/not-found.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="n">
@@ -6602,7 +6782,11 @@
           <t>No root-layout error boundary</t>
         </is>
       </c>
-      <c r="N85" s="13" t="inlineStr"/>
+      <c r="N85" s="13" t="inlineStr">
+        <is>
+          <t>app/global-error.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n">
@@ -6652,7 +6836,11 @@
           <t>part-06-flask_mt5_openapi.yaml defines 5 admin endpoints (/api/admin/terminals/health, /stats, /{id}/logs, /{id}/restart, /restart-all) with ZERO UI. Operationally significant given the current flask-api outage.</t>
         </is>
       </c>
-      <c r="N86" s="13" t="inlineStr"/>
+      <c r="N86" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/terminals/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n">
@@ -6702,7 +6890,11 @@
           <t>8 cron endpoints exist (/api/cron/*); no run history, no manual trigger, no failure visibility.</t>
         </is>
       </c>
-      <c r="N87" s="13" t="inlineStr"/>
+      <c r="N87" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/jobs/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n">
@@ -6752,7 +6944,11 @@
           <t>OutboxEvent model + OutboxPublisherCron are live in production; no UI shows PENDING / PROCESSING / FAILED events.</t>
         </is>
       </c>
-      <c r="N88" s="13" t="inlineStr"/>
+      <c r="N88" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/outbox/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n">
@@ -6802,7 +6998,11 @@
           <t>SystemConfigHistory model has zero UI - no audit view of who changed which config.</t>
         </is>
       </c>
-      <c r="N89" s="13" t="inlineStr"/>
+      <c r="N89" s="13" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/config-history/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
@@ -6852,7 +7052,11 @@
           <t>No way to send a platform-wide notification despite the Notification model supporting it.</t>
         </is>
       </c>
-      <c r="N90" s="13" t="inlineStr"/>
+      <c r="N90" s="13" t="inlineStr">
+        <is>
+          <t>Pending Codebase Creation</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="n">
@@ -6902,7 +7106,11 @@
           <t>cron/send-monthly-reports generates statements; no in-product archive.</t>
         </is>
       </c>
-      <c r="N91" s="13" t="inlineStr"/>
+      <c r="N91" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/dashboard/statements/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="n">
@@ -6952,7 +7160,11 @@
           <t>Banners, assets, link builder - standard for affiliate programmes, absent here.</t>
         </is>
       </c>
-      <c r="N92" s="13" t="inlineStr"/>
+      <c r="N92" s="13" t="inlineStr">
+        <is>
+          <t>app/affiliate/dashboard/resources/page.tsx</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N92"/>
@@ -6966,7 +7178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7014,6 +7226,16 @@
           <t>Verdict</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Current Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Verified Consumer / Disposition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
@@ -7049,6 +7271,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>WIRE IN PHASE 7</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>lib/api/index.ts (wire in Phase 7)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
@@ -7084,6 +7316,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WIRE IN PHASE 7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>lib/api/index.ts + /test-api (wire in Phase 7)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -7119,6 +7361,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>WIRE IN PHASE 7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>/settings/billing cancel dialog</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -7154,6 +7406,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>app/(public)/settings/account/delete/confirm/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -7189,6 +7451,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>app/(public)/settings/account/delete/cancel/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -7224,6 +7496,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>app/checkout/return/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -7259,6 +7541,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DECIDED - BY DESIGN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Session 6-8 CONFIRM - DiscountCodeInput consumes validate-discount</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -7294,6 +7586,16 @@
           <t>WIRE or DELETE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DECIDED - BY DESIGN</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Session 6-8 CONFIRM - PriceDisplay uses /convert server-side math</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -7329,6 +7631,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/affiliates/reports/code-flows/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -7364,6 +7676,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/affiliates/reports/code-inventory/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -7399,6 +7721,16 @@
           <t>WIRE - CRITICAL</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/fraud-alerts/[id]/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -7434,6 +7766,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>app/affiliate/dashboard/code-inventory/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -7469,6 +7811,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DECIDED - KEEP</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Phase 8 deletion sweep (Verification Sheet Row 24)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -7504,6 +7856,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/alerts/page.tsx &amp; /alerts/new/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
@@ -7539,6 +7901,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/alerts/page.tsx &amp; /charts/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
@@ -7574,6 +7946,16 @@
           <t>WIRE</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/charts/[symbol]/[timeframe]/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
@@ -7609,6 +7991,16 @@
           <t>CREATE ROUTE</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Geo detection fallback handled cleanly in pricing page</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
@@ -7644,6 +8036,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/settings/security/activity/page.tsx + settings/security/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
@@ -7679,6 +8081,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/users/[id]/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -7714,6 +8126,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>app/(public)/settings/account/delete/* &amp; app/(dashboard)/settings/account/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
@@ -7749,6 +8171,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/config-history/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
@@ -7784,6 +8216,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>app/affiliate/dashboard/payouts/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -7819,6 +8261,16 @@
           <t>EXTEND</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/batches/[batchId]/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -7854,6 +8306,16 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/disbursement/audit/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -7889,6 +8351,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/outbox/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
@@ -7924,6 +8396,16 @@
           <t>WIRE - PRO advertises a 7-day trial</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/settings/billing/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
@@ -7959,6 +8441,16 @@
           <t>BUILD PAGE</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/terminals/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
@@ -7994,6 +8486,16 @@
           <t>OPTIONAL</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>BUILT / CLOSED</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/admin/system/jobs/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -8029,6 +8531,16 @@
           <t>DEAD CODE - DELETE</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CLOSED / SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Superseded by live /api/user/2fa/* endpoints</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -8064,6 +8576,16 @@
           <t>BY DESIGN - not a gap</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>BY DESIGN</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Chart WebSocket hooks use-ohlcv-socket.ts</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -8099,6 +8621,16 @@
           <t>DEV ONLY</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DEV ONLY</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Dev seed utility /api/test/seed</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
@@ -8132,6 +8664,16 @@
       <c r="G33" s="14" t="inlineStr">
         <is>
           <t>BY DESIGN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>BY DESIGN</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Stripe &amp; RiseWorks provider webhooks</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8183,6 +8725,16 @@
           <t>Fix</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Current Status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Verified Code Location / Resolution</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
@@ -8208,6 +8760,16 @@
           <t>REMOVE - not a V8 product concept</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Removed unneeded link from components/layout/sidebar.tsx &amp; mobile-nav.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
@@ -8233,6 +8795,16 @@
           <t>REMOVE - not a V8 product concept</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Removed unneeded link from components/layout/sidebar.tsx &amp; mobile-nav.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -8258,6 +8830,16 @@
           <t>BUILD PAGE (A2-1)</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>app/(dashboard)/notifications/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -8283,6 +8865,16 @@
           <t>BUILD PAGE (B-01)</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>app/(marketing)/about/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -8308,6 +8900,16 @@
           <t>BUILD PAGE (B-02)</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>app/(marketing)/docs/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -8333,6 +8935,16 @@
           <t>BUILD PAGE (B-03)</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>app/(marketing)/blog/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -8358,6 +8970,16 @@
           <t>BUILD PAGE (B-04)</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>app/(marketing)/changelog/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -8383,6 +9005,16 @@
           <t>BUILD PAGE (B-05)</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>app/(marketing)/careers/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -8408,6 +9040,16 @@
           <t>BUILD PAGE (B-06) - compliance-relevant</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>app/(marketing)/disclaimer/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -8433,6 +9075,16 @@
           <t>BUILD PUBLIC PAGE (B-07)</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>app/(marketing)/terms/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -8458,6 +9110,16 @@
           <t>BUILD PUBLIC PAGE (B-08)</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>app/(marketing)/privacy/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -8483,6 +9145,16 @@
           <t>BUILD PAGE (B-09)</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>app/(marketing)/help/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -8508,6 +9180,16 @@
           <t>BUILD PAGE (B-10)</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>app/affiliate/page.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -8531,6 +9213,16 @@
       <c r="E15" s="13" t="inlineStr">
         <is>
           <t>BUILD or REDIRECT to /affiliate/register (B-11)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BUILT</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>app/affiliate/join/page.tsx</t>
         </is>
       </c>
     </row>
